--- a/annotations/review_20.xlsx
+++ b/annotations/review_20.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="人工复核表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="复核摘要" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人工复核表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="复核摘要" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,11 +519,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>存在夸大功效</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>独立女主 || 近30天低价</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>不适用</t>
@@ -578,11 +582,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>存在夸大功效</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>即刻紧致少女如春 || 重塑私密「年轻态」</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>否</t>
@@ -647,7 +655,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>色域天花板 || 行业唯一</t>
+          <t>行业唯一、色域天花板</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -777,7 +785,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>95%以上的皮肤问题都是你晒出来的 || 防晒不到位，肌肤老10倍 || 防晒不到位，肌肤老10倍 || 防晒不到位，肌肤老10倍 || 防晒不到位，肌肤老10倍 || 防晒不到位，肌肤老10倍 || 防晒不到位，肌肤老10倍 || 防晒不到位，肌肤老10倍 || 防晒不到位，肌肤老10倍 || 防晒不到位，肌肤老10倍</t>
+          <t>95%以上的皮肤问题都是你晒出来的 || 防晒不到位 肌肤老10倍</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -899,7 +907,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>全国包邮赠送 || 权成实测肌肤更紧·更弹·更亮</t>
+          <t>行业天花板 || 权威实测肌肤更紧·更弹·更亮 || 最后几单</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -956,7 +964,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>存在诱导消费</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -964,7 +972,11 @@
           <t>…材，一定要我选黑色。身材匀称，选白色。对，全都是最低价了，这个上衣肚大必须给你穿。宝贝儿，我跟你讲，我… || 最低价了是吧珊珊</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>全都是最低价了</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>是</t>
@@ -1029,7 +1041,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>最后最后十4箱630个名额</t>
+          <t>最后最后十4箱630个名额 || 行业天花板</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1081,16 +1093,24 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>存在夸大功效</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>存在夸大功效</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>首创者</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>源头抑黑更温和不 || 连续5年销量NO1</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>否</t>
@@ -1203,22 +1223,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>存在诱导消费</t>
+          <t>存在诱导消费；存在夸大功效</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>存在诱导消费</t>
+          <t>存在夸大功效；存在诱导消费</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>…为这个右上这个券到10点完就没了。你现在买不仅能全年最低价，全年送最多。王总说给你多加5个亮白精华免费7天…</t>
+          <t>…为这个右上这个券到10点完就没了。你现在买不仅能全年最低价，全年送最多。王总说给你多加5个亮白精华免费7天… || 首创者</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>全年最低价</t>
+          <t>全年最低价 || 最后几单 || 14天改善10大纹路14天真人评估 || 全球自研环六肽首创者</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1275,7 +1295,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>存在夸大功效</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1283,7 +1303,11 @@
           <t>行业省钱天花板一天不到5分钱</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>行业省钱天花板一天不到5分钱</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>是</t>
@@ -1338,11 +1362,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>存在夸大功效</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>上天要链接红梅大礼盒520福利，总监空降开价618抢限购，现拍下不要399，全部48小时内现货速发，想送妈妈期沐好一份特别礼物，就选韩束红梅礼盒拍要链接全发正宗每单都是幸运大礼盒，送红苗痛快150券，150升入50个大面霜，总肩空降，再送3小时防晒，外再送美白蛋白 || 今天只，错过不再</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>否</t>
@@ -1466,7 +1494,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>行业天花板 || 0乳糖 || 0元送 || 1.6亿罐</t>
+          <t>行业天花板 || 长肌肉 || 最后几单</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1533,7 +1561,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>今天保证给大家历史最低价不反复不依赖 || 早上卖完断货 || 2000%*直入肺源呵护 || 20倍高吸收率</t>
+          <t>今天保证给大家历史最低价不反复不依赖 || 今天这一批货呢，最后一批最后一批卖完就断货 || 早上卖完断货 || 2000%*直入肺源呵护 || 20倍高吸收率 || 入防草本费芝</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1585,7 +1613,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>存在夸大功效</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1593,10 +1621,14 @@
           <t>存在夸大功效</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>…析进一步产生了不同氨糖的区别。研究证实，盐酸氨糖治疗骨关节炎效应量仅0.06，几乎无效，而硫酸氨糖效… || …而硫酸氨糖效应量优于盐酸氨糖可达0.4氨糖就缓解治疗关节这个里面我们不涉及到治疗。现在的视频里面会说… || …可达0.4氨糖就缓解治疗关节这个里面我们不涉及到治疗。现在的视频里面会说到提到这个治疗的这个问题。但… || …面我们不涉及到治疗。现在的视频里面会说到提到这个治疗的这个问题</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>可达0.4</t>
+          <t>可达0.44</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1659,7 +1691,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>唯一的副作用就是让你变得太好看了 || 不红不肿，不脱皮 || 7分钟快速褪红4天 || 改善泛红，焕亮，弹嫩</t>
+          <t>唯一的副作用就是让你变得太好看了 || 三天见效</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1722,7 +1754,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>带来好运</t>
+          <t>紫气东来、紫禁城、紫微星、紫气代表着尊贵和好运</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1774,16 +1806,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>存在夸大功效</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+          <t>存在夸大功效</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>国内首个线上AI测肤功能</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>国内首个线上AI测肤功能 || 一人一方</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>否</t>
@@ -1843,10 +1883,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>…南，耳机真的不是越贵越好，大部分学生党的耳机价格天花板也就几百块了。而我们使用耳机的寿命也就两三年。这… || 天花板也就几百块了</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>…南，耳机真的不是越贵越好，大部分学生党的耳机价格天花板也就几百块了。而我们使用耳机的寿命也就两三年。这… || 首创双边四动圈 || 天花板也就几百块了</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>最后几单</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>否</t>
@@ -1886,12 +1930,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>稀有标签「无法判断」</t>
+          <t>口播为空的负例</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>无法判断</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1901,24 +1945,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>无法判断</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>不适用</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1928,12 +1972,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>口播几乎为空、画面无风险原文。规则无命中即出「正常」；模型按证据不足出「无法判断」。</t>
+          <t>口播为空、画面无风险原文。金标准不设无法判断，两边均标正常。</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>口播为空，画面未见「首创」或其它虚假宣传原文，证据不足。</t>
+          <t>口播为空，画面未见「首创」或其它虚假宣传原文；金标准不设无法判断，标正常。</t>
         </is>
       </c>
     </row>
@@ -1970,7 +2014,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>真的特别管用的整容与变美斜招 || 最后几单</t>
+          <t>真的特别管用的整容与变美斜招</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2047,7 +2091,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -2077,7 +2121,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
